--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488046_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488046_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.732</v>
+        <v>11.5498</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8929</v>
+        <v>8.3004</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8391</v>
+        <v>3.2494</v>
       </c>
       <c r="G2" t="n">
         <v>7.7519</v>
@@ -610,13 +610,13 @@
         <v>2.5769</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7997</v>
+        <v>0.6175</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4881</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2878</v>
+        <v>0.6982</v>
       </c>
       <c r="V2" t="n">
         <v>0.6036</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>11.4234</v>
+        <v>7.9834</v>
       </c>
       <c r="E3" t="n">
-        <v>10.3885</v>
+        <v>7.7628</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0349</v>
+        <v>0.2206</v>
       </c>
       <c r="G3" t="n">
         <v>5.1091</v>
@@ -688,13 +688,13 @@
         <v>1.9822</v>
       </c>
       <c r="S3" t="n">
-        <v>5.4442</v>
+        <v>2.0042</v>
       </c>
       <c r="T3" t="n">
-        <v>4.0896</v>
+        <v>1.4639</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3546</v>
+        <v>0.5403</v>
       </c>
       <c r="V3" t="n">
         <v>0.8701</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.7114</v>
+        <v>6.6553</v>
       </c>
       <c r="E4" t="n">
         <v>4.1635</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5479</v>
+        <v>2.4918</v>
       </c>
       <c r="G4" t="n">
         <v>5.1307</v>
@@ -766,13 +766,13 @@
         <v>2.1805</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4617</v>
+        <v>0.4056</v>
       </c>
       <c r="T4" t="n">
         <v>0.202</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2597</v>
+        <v>0.2036</v>
       </c>
       <c r="V4" t="n">
         <v>-0.0704</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. PAÑOS HUERTAS</t>
+          <t>B. GARCIA ALVAREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5107</v>
+        <v>2.1523</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5107</v>
+        <v>2.5952</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0.4429</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5107</v>
+        <v>1.5924</v>
       </c>
       <c r="H5" t="n">
-        <v>0.908</v>
+        <v>1.5522</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6027</v>
+        <v>0.0402</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5107</v>
+        <v>1.8818</v>
       </c>
       <c r="K5" t="n">
-        <v>0.908</v>
+        <v>1.8702</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6027</v>
+        <v>0.0117</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-0.2895</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.318</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.0285</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.3964</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.3787</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0.1735</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.0148</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.1883</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.6808</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.3438</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. GARCIA ALVAREZ</t>
+          <t>L. PAÑOS HUERTAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0722</v>
+        <v>1.5107</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6555</v>
+        <v>1.5107</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5833</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5924</v>
+        <v>1.5107</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5522</v>
+        <v>0.908</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0402</v>
+        <v>0.6027</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8818</v>
+        <v>1.5107</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8702</v>
+        <v>0.908</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0117</v>
+        <v>0.6027</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2895</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.318</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0285</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3964</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3787</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2536</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9249000000000001</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3287</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.6808</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.3438</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2074</v>
+        <v>1.1784</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0598</v>
+        <v>0.5743</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2672</v>
+        <v>0.6041</v>
       </c>
       <c r="G7" t="n">
         <v>1.0787</v>
@@ -1000,13 +1000,13 @@
         <v>1.5858</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0785</v>
+        <v>-0.1074</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8001</v>
+        <v>-0.166</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2783</v>
+        <v>0.0586</v>
       </c>
       <c r="V7" t="n">
         <v>0.6036</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4116</v>
+        <v>0.0063</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4191</v>
+        <v>-1.1135</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0075</v>
+        <v>1.1198</v>
       </c>
       <c r="G8" t="n">
         <v>0.7653</v>
@@ -1078,13 +1078,13 @@
         <v>0.7929</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9786</v>
+        <v>-0.5607</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3744</v>
+        <v>-0.0688</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6042999999999999</v>
+        <v>-0.4919</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. VAN BRANDWIJK</t>
+          <t>R. HIDALGO SALAZAR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6731</v>
+        <v>-0.8662</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2205</v>
+        <v>-1.2591</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5474</v>
+        <v>0.3929</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1816</v>
+        <v>-1.1324</v>
       </c>
       <c r="H9" t="n">
         <v>-0.5891</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4075</v>
+        <v>-0.5433</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.659</v>
+        <v>-1.3381</v>
       </c>
       <c r="K9" t="n">
         <v>-0.659</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.6791</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4774</v>
+        <v>0.2057</v>
       </c>
       <c r="N9" t="n">
         <v>0.0699</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4075</v>
+        <v>0.1358</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3964</v>
+        <v>0.5947</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0.5947</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.095</v>
+        <v>-0.3285</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4295</v>
+        <v>0.0789</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5246</v>
+        <v>-0.4075</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. HIDALGO SALAZAR</t>
+          <t>K. VAN BRANDWIJK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.07</v>
+        <v>-0.9506</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4629</v>
+        <v>-1.5261</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3929</v>
+        <v>0.5755</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1324</v>
+        <v>-0.1816</v>
       </c>
       <c r="H10" t="n">
         <v>-0.5891</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5433</v>
+        <v>0.4075</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3381</v>
+        <v>-0.659</v>
       </c>
       <c r="K10" t="n">
         <v>-0.659</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6791</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2057</v>
+        <v>0.4774</v>
       </c>
       <c r="N10" t="n">
         <v>0.0699</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1358</v>
+        <v>0.4075</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5947</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R10" t="n">
         <v>0.5947</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5323</v>
+        <v>-0.3726</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1248</v>
+        <v>0.1239</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4075</v>
+        <v>-0.4965</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.273</v>
+        <v>-1.3644</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7296</v>
+        <v>-1.9333</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4566</v>
+        <v>0.5689</v>
       </c>
       <c r="G11" t="n">
         <v>0.7887999999999999</v>
@@ -1312,13 +1312,13 @@
         <v>0.9911</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6695</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6902</v>
+        <v>0.4864</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0206</v>
+        <v>0.0917</v>
       </c>
       <c r="V11" t="n">
         <v>-1.7403</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0232</v>
+        <v>-1.6071</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6154</v>
+        <v>-1.5925</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4077</v>
+        <v>-0.0146</v>
       </c>
       <c r="G12" t="n">
         <v>0.7907</v>
@@ -1390,13 +1390,13 @@
         <v>1.1893</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6225000000000001</v>
+        <v>-0.2065</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0696</v>
+        <v>-0.0467</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5528999999999999</v>
+        <v>-0.1598</v>
       </c>
       <c r="V12" t="n">
         <v>-0.4074</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.8557</v>
+        <v>-2.0312</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.5214</v>
+        <v>-4.9496</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6657</v>
+        <v>2.9184</v>
       </c>
       <c r="G13" t="n">
         <v>-2.2312</v>
@@ -1468,13 +1468,13 @@
         <v>2.3787</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0209</v>
+        <v>-0.1964</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7267</v>
+        <v>-0.155</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2942</v>
+        <v>-0.0415</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.8288</v>
+        <v>-3.071</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.8403</v>
+        <v>-4.1667</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0115</v>
+        <v>1.0957</v>
       </c>
       <c r="G14" t="n">
         <v>-1.1107</v>
@@ -1546,13 +1546,13 @@
         <v>1.5858</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.28</v>
+        <v>-0.5222</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8736</v>
+        <v>-0.1999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4065</v>
+        <v>-0.3222</v>
       </c>
       <c r="V14" t="n">
         <v>0.9405</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>20.5217</v>
+        <v>21.1457</v>
       </c>
       <c r="E15" t="n">
-        <v>7.742099999999996</v>
+        <v>8.366100000000003</v>
       </c>
       <c r="F15" t="n">
-        <v>12.7797</v>
+        <v>12.7796</v>
       </c>
       <c r="G15" t="n">
         <v>19.8624</v>
@@ -1615,7 +1615,7 @@
         <v>2.8877</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.991099999999999</v>
+        <v>-0.9910999999999994</v>
       </c>
       <c r="Q15" t="n">
         <v>-19.8221</v>
@@ -1624,13 +1624,13 @@
         <v>18.8313</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5137</v>
+        <v>1.1376</v>
       </c>
       <c r="T15" t="n">
-        <v>1.029099999999999</v>
+        <v>1.6528</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5154999999999993</v>
+        <v>-0.5152999999999998</v>
       </c>
       <c r="V15" t="n">
         <v>1.1367</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.6762</v>
+        <v>5.112</v>
       </c>
       <c r="E16" t="n">
-        <v>6.3716</v>
+        <v>5.7604</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6954</v>
+        <v>-0.6484</v>
       </c>
       <c r="G16" t="n">
         <v>-1.3863</v>
@@ -1702,13 +1702,13 @@
         <v>2.9733</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9258</v>
+        <v>0.3616</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8849</v>
+        <v>0.2737</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0409</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>4.1545</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.709</v>
+        <v>2.3751</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3029</v>
+        <v>0.6085</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4062</v>
+        <v>1.7666</v>
       </c>
       <c r="G18" t="n">
         <v>0.8882</v>
@@ -1858,13 +1858,13 @@
         <v>1.5858</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6945</v>
+        <v>-0.0284</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2899</v>
+        <v>0.0157</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4046</v>
+        <v>-0.0441</v>
       </c>
       <c r="V18" t="n">
         <v>-0.0704</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6802</v>
+        <v>0.6626</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7293</v>
+        <v>1.6275</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0491</v>
+        <v>-0.9649</v>
       </c>
       <c r="G19" t="n">
         <v>3.2077</v>
@@ -1936,13 +1936,13 @@
         <v>1.3876</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2654</v>
+        <v>0.2478</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2423</v>
+        <v>0.1405</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0231</v>
+        <v>0.1073</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2071</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1459</v>
+        <v>-0.3027</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2195</v>
+        <v>-2.4232</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0736</v>
+        <v>2.1206</v>
       </c>
       <c r="G20" t="n">
         <v>-3.0666</v>
@@ -2014,13 +2014,13 @@
         <v>2.1805</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8414</v>
+        <v>0.6846</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5178</v>
+        <v>0.3141</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3236</v>
+        <v>0.3706</v>
       </c>
       <c r="V20" t="n">
         <v>1.8811</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4705</v>
+        <v>-1.2397</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.082</v>
+        <v>-1.7951</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6115</v>
+        <v>0.5553</v>
       </c>
       <c r="G21" t="n">
         <v>1.2784</v>
@@ -2092,13 +2092,13 @@
         <v>2.1805</v>
       </c>
       <c r="S21" t="n">
-        <v>1.5594</v>
+        <v>0.7901</v>
       </c>
       <c r="T21" t="n">
-        <v>1.7585</v>
+        <v>1.0454</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1991</v>
+        <v>-0.2553</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5331</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2303</v>
+        <v>-2.3883</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9971</v>
+        <v>-2.099</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2331</v>
+        <v>-0.2893</v>
       </c>
       <c r="G22" t="n">
         <v>-2.7243</v>
@@ -2170,13 +2170,13 @@
         <v>1.784</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2342</v>
+        <v>0.0762</v>
       </c>
       <c r="T22" t="n">
-        <v>0.191</v>
+        <v>0.0891</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0432</v>
+        <v>-0.0129</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5331</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.4588</v>
+        <v>-5.5861</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6013</v>
+        <v>-1.4994</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.8575</v>
+        <v>-4.0867</v>
       </c>
       <c r="G23" t="n">
         <v>-3.1807</v>
@@ -2248,13 +2248,13 @@
         <v>1.5858</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.192</v>
+        <v>-0.3193</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.756</v>
+        <v>-0.6541</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.3348</v>
       </c>
       <c r="V23" t="n">
         <v>-2.6808</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.0994</v>
+        <v>-5.8443</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.4751</v>
+        <v>-4.6601</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6243</v>
+        <v>-1.1842</v>
       </c>
       <c r="G24" t="n">
         <v>-4.5834</v>
@@ -2326,13 +2326,13 @@
         <v>2.1805</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.7231</v>
+        <v>-0.468</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.4351</v>
+        <v>-0.6202</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2879</v>
+        <v>0.1522</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.4584</v>
+        <v>-7.0803</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.3133</v>
+        <v>-4.2114</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.1451</v>
+        <v>-2.8689</v>
       </c>
       <c r="G25" t="n">
         <v>-4.7744</v>
@@ -2404,13 +2404,13 @@
         <v>1.5858</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.4863</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6864</v>
+        <v>-0.5845</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1781</v>
+        <v>0.0982</v>
       </c>
       <c r="V25" t="n">
         <v>-2.4142</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.739800000000001</v>
+        <v>-7.8876</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.5112</v>
+        <v>-7.1038</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.2285</v>
+        <v>-0.7838000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-8.536899999999999</v>
@@ -2482,13 +2482,13 @@
         <v>2.3787</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.8659</v>
+        <v>-0.0137</v>
       </c>
       <c r="T26" t="n">
-        <v>0.0883</v>
+        <v>0.4957</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.9540999999999999</v>
+        <v>-0.5094</v>
       </c>
       <c r="V26" t="n">
         <v>0.2666</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-20.5217</v>
+        <v>-19.1633</v>
       </c>
       <c r="E27" t="n">
-        <v>-12.7797</v>
+        <v>-12.7796</v>
       </c>
       <c r="F27" t="n">
-        <v>-7.7417</v>
+        <v>-6.3837</v>
       </c>
       <c r="G27" t="n">
         <v>-19.8623</v>
@@ -2560,13 +2560,13 @@
         <v>19.8225</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.5137000000000003</v>
+        <v>0.8445999999999998</v>
       </c>
       <c r="T27" t="n">
-        <v>0.5154</v>
+        <v>0.5154000000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.029</v>
+        <v>0.3292999999999999</v>
       </c>
       <c r="V27" t="n">
         <v>-1.136500000000001</v>
